--- a/data/HCA_cluster_validation.xlsx
+++ b/data/HCA_cluster_validation.xlsx
@@ -604,13 +604,13 @@
         <v>2</v>
       </c>
       <c r="C13">
-        <v>0.266</v>
+        <v>0.281</v>
       </c>
       <c r="D13">
-        <v>176</v>
+        <v>239</v>
       </c>
       <c r="E13">
-        <v>543</v>
+        <v>480</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -621,13 +621,13 @@
         <v>3</v>
       </c>
       <c r="C14">
-        <v>0.34</v>
+        <v>0.375</v>
       </c>
       <c r="D14">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="E14">
-        <v>363</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -638,13 +638,13 @@
         <v>4</v>
       </c>
       <c r="C15">
-        <v>0.398</v>
+        <v>0.388</v>
       </c>
       <c r="D15">
-        <v>159</v>
+        <v>75</v>
       </c>
       <c r="E15">
-        <v>204</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -655,13 +655,13 @@
         <v>5</v>
       </c>
       <c r="C16">
-        <v>0.421</v>
+        <v>0.414</v>
       </c>
       <c r="D16">
         <v>66</v>
       </c>
       <c r="E16">
-        <v>180</v>
+        <v>239</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -672,13 +672,13 @@
         <v>6</v>
       </c>
       <c r="C17">
-        <v>0.447</v>
+        <v>0.436</v>
       </c>
       <c r="D17">
         <v>31</v>
       </c>
       <c r="E17">
-        <v>180</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -689,13 +689,13 @@
         <v>7</v>
       </c>
       <c r="C18">
-        <v>0.462</v>
+        <v>0.455</v>
       </c>
       <c r="D18">
         <v>31</v>
       </c>
       <c r="E18">
-        <v>180</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -706,13 +706,13 @@
         <v>8</v>
       </c>
       <c r="C19">
-        <v>0.492</v>
+        <v>0.473</v>
       </c>
       <c r="D19">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E19">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="F19" t="s">
         <v>7</v>
@@ -726,13 +726,13 @@
         <v>9</v>
       </c>
       <c r="C20">
-        <v>0.507</v>
+        <v>0.499</v>
       </c>
       <c r="D20">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E20">
-        <v>176</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -743,13 +743,13 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.524</v>
+        <v>0.516</v>
       </c>
       <c r="D21">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E21">
-        <v>176</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -760,10 +760,10 @@
         <v>11</v>
       </c>
       <c r="C22">
-        <v>0.536</v>
+        <v>0.543</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E22">
         <v>176</v>
@@ -777,10 +777,10 @@
         <v>12</v>
       </c>
       <c r="C23">
-        <v>0.556</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="D23">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E23">
         <v>176</v>

--- a/data/HCA_cluster_validation.xlsx
+++ b/data/HCA_cluster_validation.xlsx
@@ -11,38 +11,6 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="9">
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>Silhouette</t>
-  </si>
-  <si>
-    <t>Min_n</t>
-  </si>
-  <si>
-    <t>Max_n</t>
-  </si>
-  <si>
-    <t>Selected</t>
-  </si>
-  <si>
-    <t>Institutions</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>CBSAs</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -386,29 +354,43 @@
   <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>6</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Silhouette</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Min_n</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Max_n</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Selected</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
       </c>
       <c r="B2">
         <v>2</v>
@@ -423,9 +405,11 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>6</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
       </c>
       <c r="B3">
         <v>3</v>
@@ -440,9 +424,11 @@
         <v>924</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>6</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
       </c>
       <c r="B4">
         <v>4</v>
@@ -457,9 +443,11 @@
         <v>924</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>6</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
       </c>
       <c r="B5">
         <v>5</v>
@@ -474,9 +462,11 @@
         <v>746</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>6</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
       </c>
       <c r="B6">
         <v>6</v>
@@ -491,9 +481,11 @@
         <v>746</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>6</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
       </c>
       <c r="B7">
         <v>7</v>
@@ -508,9 +500,11 @@
         <v>746</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>6</v>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
       </c>
       <c r="B8">
         <v>8</v>
@@ -525,9 +519,11 @@
         <v>746</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>6</v>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
       </c>
       <c r="B9">
         <v>9</v>
@@ -541,13 +537,17 @@
       <c r="E9">
         <v>746</v>
       </c>
-      <c r="F9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>6</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
       </c>
       <c r="B10">
         <v>10</v>
@@ -562,9 +562,11 @@
         <v>746</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>6</v>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
       </c>
       <c r="B11">
         <v>11</v>
@@ -579,9 +581,11 @@
         <v>746</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
-        <v>6</v>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
       </c>
       <c r="B12">
         <v>12</v>
@@ -596,194 +600,218 @@
         <v>492</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>8</v>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CBSAs</t>
+        </is>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>0.281</v>
+        <v>0.322</v>
       </c>
       <c r="D13">
-        <v>239</v>
+        <v>191</v>
       </c>
       <c r="E13">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
-        <v>8</v>
+        <v>528</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CBSAs</t>
+        </is>
       </c>
       <c r="B14">
         <v>3</v>
       </c>
       <c r="C14">
-        <v>0.375</v>
+        <v>0.407</v>
       </c>
       <c r="D14">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E14">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>8</v>
+        <v>339</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CBSAs</t>
+        </is>
       </c>
       <c r="B15">
         <v>4</v>
       </c>
       <c r="C15">
-        <v>0.388</v>
+        <v>0.472</v>
       </c>
       <c r="D15">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E15">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
-        <v>8</v>
+        <v>268</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CBSAs</t>
+        </is>
       </c>
       <c r="B16">
         <v>5</v>
       </c>
       <c r="C16">
-        <v>0.414</v>
+        <v>0.509</v>
       </c>
       <c r="D16">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E16">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
-        <v>8</v>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CBSAs</t>
+        </is>
       </c>
       <c r="B17">
         <v>6</v>
       </c>
       <c r="C17">
-        <v>0.436</v>
+        <v>0.531</v>
       </c>
       <c r="D17">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E17">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
-        <v>8</v>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CBSAs</t>
+        </is>
       </c>
       <c r="B18">
         <v>7</v>
       </c>
       <c r="C18">
-        <v>0.455</v>
+        <v>0.549</v>
       </c>
       <c r="D18">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E18">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" t="s">
-        <v>8</v>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CBSAs</t>
+        </is>
       </c>
       <c r="B19">
         <v>8</v>
       </c>
       <c r="C19">
-        <v>0.473</v>
+        <v>0.569</v>
       </c>
       <c r="D19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E19">
-        <v>208</v>
-      </c>
-      <c r="F19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" t="s">
-        <v>8</v>
+        <v>191</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CBSAs</t>
+        </is>
       </c>
       <c r="B20">
         <v>9</v>
       </c>
       <c r="C20">
-        <v>0.499</v>
+        <v>0.592</v>
       </c>
       <c r="D20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E20">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" t="s">
-        <v>8</v>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CBSAs</t>
+        </is>
       </c>
       <c r="B21">
         <v>10</v>
       </c>
       <c r="C21">
-        <v>0.516</v>
+        <v>0.604</v>
       </c>
       <c r="D21">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E21">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" t="s">
-        <v>8</v>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CBSAs</t>
+        </is>
       </c>
       <c r="B22">
         <v>11</v>
       </c>
       <c r="C22">
-        <v>0.543</v>
+        <v>0.614</v>
       </c>
       <c r="D22">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E22">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" t="s">
-        <v>8</v>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CBSAs</t>
+        </is>
       </c>
       <c r="B23">
         <v>12</v>
       </c>
       <c r="C23">
-        <v>0.5629999999999999</v>
+        <v>0.626</v>
       </c>
       <c r="D23">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E23">
-        <v>176</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
